--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SP.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_SP.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R37f85d803ac94fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rb30929b340b247d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rf4b4e83aa9ee4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Re248567b697342a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Re8080c1fdbfb4298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R4891801269534578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R00a131aede6e4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R1bcc03a9c919492e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Re08dc20fb04941e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R0308ff3ae50b4289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R3dad639fd6e842ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R779c947cc1294cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rb5a0e9f98d014818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R5e141d8deff045f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R5f1074e118a84de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R6ed10ff2dd7f4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R611fcc515dd1474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R8ed3447a7a354d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rd75da070384a49c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R7c95319f396d4f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R62a053b71d6a4035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R965d33e7023f48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R842bec3abb0149b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rdb862cd48fd44b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R61bdb2f358b04629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R5de87127c6f54bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R28d8b74005ce419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R0fe40c50490747bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R69ea41e95e0c47e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R473f4a809bee4dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rfd521aeccc674a21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rd61cc29e99114e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R9992afd594054a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R45c51a441f47474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R123e9bf0f3dd476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R1d62b78e56864e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R30185fcfda894d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rcbba4cf9a5aa4aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R56fa5dee6a3f4e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rfe2099f7ea164dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R26ce0df25db14684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Raac76c0f6ef44492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Rcdc0e46ab9404768"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3008,6 +3009,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>マルガリーテ・ブラント</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>？？？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
